--- a/map.xlsx
+++ b/map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liul3\Desktop\旭日图自动生成工具\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B80DE1D-F238-45EF-B3E1-42B8E6C613A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9E0F7A-F4C2-45AD-8773-BF7F0C407DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-600" yWindow="1230" windowWidth="15420" windowHeight="7370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,12 +71,6 @@
     <t>IIT</t>
   </si>
   <si>
-    <t>study NSADR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">study SADR </t>
-  </si>
-  <si>
     <t>镁信</t>
   </si>
   <si>
@@ -120,10 +114,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>others</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>literature</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -132,6 +122,18 @@
   </si>
   <si>
     <t>903SADR</t>
+  </si>
+  <si>
+    <t>505 study</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>903 study</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMK study</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -197,15 +199,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -512,25 +521,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="26" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26" style="2" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -538,221 +547,278 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6">
+        <v>400</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="6">
+        <v>128</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6">
+        <v>123</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6">
+        <v>111</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6">
+        <v>120</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6">
+        <v>117</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6">
+        <v>119</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3">
-        <v>400</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3">
-        <v>128</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="3">
-        <v>123</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="3">
-        <v>111</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="6">
+        <v>903</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="3">
-        <v>903</v>
-      </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="3">
+      <c r="C24" s="6">
         <v>505</v>
       </c>
-      <c r="D21" t="s">
-        <v>25</v>
-      </c>
+      <c r="D24" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15" xr:uid="{8623DCB2-28CD-4175-AC64-81D20147C00A}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{8623DCB2-28CD-4175-AC64-81D20147C00A}">
       <formula1>"400,反馈,MI,舆情,QA,文献,镁信,医学专员,其他（需备注),MRG001-C002-IIT,CWCLL-001,ZOOM"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C20" xr:uid="{0B3130C2-F082-4D10-9C89-C22F12F524FE}">
-      <formula1>"111,111-D,111SADR,123,128,128SADR,505,505SADR,903,903SADR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/map.xlsx
+++ b/map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liul3\Desktop\旭日图自动生成工具\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wuk\Desktop\SUSAR\AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9E0F7A-F4C2-45AD-8773-BF7F0C407DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5827834E-2AB7-42C1-93CF-3B452457C6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-600" yWindow="1230" windowWidth="15420" windowHeight="7370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="32">
   <si>
     <t>产品（显示在图上）</t>
   </si>
@@ -50,24 +50,15 @@
     <t>个数（计算）（显示在图上）</t>
   </si>
   <si>
-    <t>orelabrutinib</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tafasitamab </t>
   </si>
   <si>
     <t xml:space="preserve">Zurletrectinib </t>
   </si>
   <si>
-    <t>PMK program</t>
-  </si>
-  <si>
     <t>HA</t>
   </si>
   <si>
-    <t>spontaneous</t>
-  </si>
-  <si>
     <t>IIT</t>
   </si>
   <si>
@@ -80,12 +71,6 @@
     <t>医学专员</t>
   </si>
   <si>
-    <t>MRG001-C002-IIT</t>
-  </si>
-  <si>
-    <t>ZOOM</t>
-  </si>
-  <si>
     <t>128SADR</t>
   </si>
   <si>
@@ -95,45 +80,67 @@
     <t>111-D</t>
   </si>
   <si>
-    <t>HCP</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
     <t>宜诺凯2026</t>
   </si>
   <si>
     <t>上市后研究2026</t>
   </si>
   <si>
-    <t>tafa PMK</t>
-  </si>
-  <si>
     <t>文献</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>literature</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>其他（需备注)</t>
   </si>
   <si>
     <t>903SADR</t>
   </si>
   <si>
-    <t>505 study</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>903 study</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PMK study</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>IIT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>反馈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>舆情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>QA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spontaneous</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMK Program</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PMK Study</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Literature</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Orelabrutinib</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tafa PMK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宜诺欣PMK</t>
   </si>
 </sst>
 </file>
@@ -199,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -207,15 +214,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -521,25 +521,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="26" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="4" max="4" width="34.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -547,277 +547,408 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2">
+        <v>400</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2">
+        <v>128</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="2">
+        <v>123</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="2">
+        <v>111</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="2">
+        <v>120</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="2">
+        <v>117</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="2">
+        <v>119</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2">
+        <v>400</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="2">
+        <v>903</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="2">
+        <v>400</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C36" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5" t="s">
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="6">
-        <v>400</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6" t="s">
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="6">
-        <v>128</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6">
-        <v>123</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6">
-        <v>111</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6">
-        <v>120</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6">
-        <v>117</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6">
-        <v>119</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="6">
-        <v>903</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="6">
+      <c r="C43" s="2">
         <v>505</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="5"/>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{8623DCB2-28CD-4175-AC64-81D20147C00A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8:C9 C27:C28 C39:C40" xr:uid="{8623DCB2-28CD-4175-AC64-81D20147C00A}">
       <formula1>"400,反馈,MI,舆情,QA,文献,镁信,医学专员,其他（需备注),MRG001-C002-IIT,CWCLL-001,ZOOM"</formula1>
     </dataValidation>
   </dataValidations>
